--- a/nba_defense_data.xlsx
+++ b/nba_defense_data.xlsx
@@ -497,39 +497,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20.2</v>
+        <v>17.7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="G2" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>9.9</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J2" t="n">
         <v>0.4</v>
       </c>
       <c r="K2" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="3">
@@ -540,39 +540,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.3</v>
+        <v>19.8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="G3" t="n">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="H3" t="n">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="4">
@@ -583,39 +583,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="G4" t="n">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="K4" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="5">
@@ -626,39 +626,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14.3</v>
+        <v>19.3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="G5" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="H5" t="n">
-        <v>9.6</v>
+        <v>8.5</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="6">
@@ -673,35 +673,35 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19.7</v>
+        <v>21.6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G6" t="n">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="H6" t="n">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J6" t="n">
         <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="7">
@@ -712,39 +712,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23.1</v>
+        <v>22.5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>2.4</v>
       </c>
       <c r="G7" t="n">
-        <v>5.8</v>
+        <v>7.9</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J7" t="n">
         <v>0.5</v>
       </c>
       <c r="K7" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="8">
@@ -755,39 +755,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.3</v>
+        <v>24.8</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="G8" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="H8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K8" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -798,39 +798,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20.4</v>
+        <v>23.1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G9" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="H9" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="K9" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="10">
@@ -841,39 +841,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21.3</v>
+        <v>24.6</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>2.9</v>
       </c>
       <c r="G10" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="H10" t="n">
-        <v>10.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="K10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="11">
@@ -884,36 +884,36 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24.7</v>
+        <v>22</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K11" t="n">
         <v>4</v>
@@ -927,39 +927,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25.1</v>
+        <v>23.8</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>2.9</v>
       </c>
       <c r="G12" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="H12" t="n">
-        <v>10.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="K12" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="13">
@@ -970,39 +970,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.9</v>
+        <v>24.3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="H13" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="I13" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="K13" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="14">
@@ -1013,39 +1013,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="G14" t="n">
-        <v>6.3</v>
+        <v>5.1</v>
       </c>
       <c r="H14" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="15">
@@ -1056,39 +1056,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25.5</v>
+        <v>22.5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="G15" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="H15" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="K15" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="16">
@@ -1099,39 +1099,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>25.1</v>
+        <v>26.5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="G16" t="n">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="H16" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="17">
@@ -1142,39 +1142,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.9</v>
+        <v>23.8</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G17" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="H17" t="n">
-        <v>7.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="K17" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="18">
@@ -1185,39 +1185,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>23.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="G18" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="H18" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="K18" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="19">
@@ -1228,27 +1228,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24.6</v>
+        <v>22.9</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="G19" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="H19" t="n">
         <v>8.699999999999999</v>
@@ -1257,10 +1257,10 @@
         <v>2.4</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="K19" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="20">
@@ -1271,39 +1271,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21.8</v>
+        <v>28</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="G20" t="n">
-        <v>7.1</v>
+        <v>6.3</v>
       </c>
       <c r="H20" t="n">
-        <v>6.6</v>
+        <v>7.9</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="K20" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="21">
@@ -1314,39 +1314,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23</v>
+        <v>27.1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="H21" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I21" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="K21" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="22">
@@ -1357,39 +1357,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.9</v>
+        <v>25.3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="G22" t="n">
-        <v>5.5</v>
+        <v>6.7</v>
       </c>
       <c r="H22" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="K22" t="n">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="23">
@@ -1400,39 +1400,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>21.9</v>
+        <v>24.1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="G23" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H23" t="n">
         <v>6.8</v>
       </c>
-      <c r="H23" t="n">
-        <v>9.699999999999999</v>
-      </c>
       <c r="I23" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="K23" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="24">
@@ -1443,39 +1443,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27.8</v>
+        <v>25.6</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="G24" t="n">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="H24" t="n">
-        <v>7.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="K24" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="25">
@@ -1486,39 +1486,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>26.3</v>
+        <v>25.7</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
       <c r="H25" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="I25" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="K25" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="26">
@@ -1529,27 +1529,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.8</v>
+        <v>26.3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="G26" t="n">
-        <v>7.3</v>
+        <v>6.6</v>
       </c>
       <c r="H26" t="n">
         <v>8</v>
@@ -1558,10 +1558,10 @@
         <v>2.5</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="K26" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="27">
@@ -1572,11 +1572,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>25</v>
+        <v>25.2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1585,26 +1585,26 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="G27" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="H27" t="n">
-        <v>9.4</v>
+        <v>7.9</v>
       </c>
       <c r="I27" t="n">
         <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K27" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -1615,39 +1615,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>28.7</v>
+        <v>25.8</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="G28" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="H28" t="n">
-        <v>7.6</v>
+        <v>8.9</v>
       </c>
       <c r="I28" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="K28" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="29">
@@ -1658,39 +1658,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>23.9</v>
+        <v>28.2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="G29" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="H29" t="n">
-        <v>9.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K29" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="30">
@@ -1701,39 +1701,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.9</v>
+        <v>24.5</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="F30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G30" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H30" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I30" t="n">
         <v>2.6</v>
       </c>
-      <c r="G30" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H30" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="I30" t="n">
-        <v>2</v>
-      </c>
       <c r="J30" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="31">
@@ -1748,35 +1748,35 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>30.4</v>
+        <v>27</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G31" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="H31" t="n">
-        <v>9.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J31" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K31" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
     </row>
   </sheetData>
@@ -1858,39 +1858,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19.8</v>
+        <v>23.8</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="G2" t="n">
         <v>5.8</v>
       </c>
       <c r="H2" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="I2" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="3">
@@ -1901,39 +1901,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.4</v>
+        <v>20.4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G3" t="n">
-        <v>6.3</v>
+        <v>5.3</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="4">
@@ -1944,39 +1944,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19.3</v>
+        <v>21.8</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H4" t="n">
         <v>5.4</v>
       </c>
-      <c r="H4" t="n">
-        <v>5.7</v>
-      </c>
       <c r="I4" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="K4" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="5">
@@ -1987,39 +1987,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.9</v>
+        <v>20.6</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="G5" t="n">
-        <v>7.8</v>
+        <v>5.4</v>
       </c>
       <c r="H5" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2030,39 +2030,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="K6" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="7">
@@ -2073,39 +2073,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.3</v>
+        <v>21.7</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>2.9</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="H7" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>0.5</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="8">
@@ -2116,39 +2116,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.8</v>
+        <v>23.4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="G8" t="n">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="9">
@@ -2159,39 +2159,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="G9" t="n">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
       <c r="H9" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
         <v>1.5</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K9" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="10">
@@ -2202,39 +2202,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="G10" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="H10" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="11">
@@ -2245,39 +2245,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21.9</v>
+        <v>23.2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="G11" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="H11" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K11" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="12">
@@ -2288,39 +2288,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25.6</v>
+        <v>23.3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="G12" t="n">
-        <v>4.2</v>
+        <v>8.1</v>
       </c>
       <c r="H12" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="13">
@@ -2331,39 +2331,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.4</v>
+        <v>22.6</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="G13" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="H13" t="n">
-        <v>6.3</v>
+        <v>4.1</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K13" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="14">
@@ -2374,39 +2374,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.2</v>
+        <v>22.6</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="G14" t="n">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="H14" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
         <v>0.6</v>
       </c>
       <c r="K14" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="15">
@@ -2417,39 +2417,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="G15" t="n">
-        <v>7.1</v>
+        <v>5.9</v>
       </c>
       <c r="H15" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="16">
@@ -2460,39 +2460,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.3</v>
+        <v>24.4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="G16" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="H16" t="n">
-        <v>4.1</v>
+        <v>6.3</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -2503,39 +2503,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23</v>
+        <v>23.4</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="H17" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="18">
@@ -2546,39 +2546,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>25.6</v>
+        <v>23.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="G18" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="H18" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K18" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="19">
@@ -2589,39 +2589,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24.6</v>
+        <v>23.5</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G19" t="n">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
       <c r="H19" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="K19" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="20">
@@ -2632,39 +2632,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>26.6</v>
+        <v>26.4</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="F20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K20" t="n">
         <v>3</v>
-      </c>
-      <c r="G20" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="H20" t="n">
-        <v>5</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.2</v>
       </c>
     </row>
     <row r="21">
@@ -2675,39 +2675,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>27.6</v>
+        <v>25.3</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>5.6</v>
+        <v>6.7</v>
       </c>
       <c r="H21" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="22">
@@ -2722,35 +2722,35 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>26.2</v>
+        <v>25.1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="G22" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="H22" t="n">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K22" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="23">
@@ -2761,39 +2761,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>26.8</v>
+        <v>26.1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="G23" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="H23" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K23" t="n">
-        <v>5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="24">
@@ -2804,39 +2804,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>25.2</v>
+        <v>23.7</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>3.9</v>
       </c>
       <c r="G24" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
       <c r="H24" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K24" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="25">
@@ -2847,39 +2847,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.3</v>
+        <v>25.9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>84.1</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="G25" t="n">
-        <v>5.6</v>
+        <v>6.7</v>
       </c>
       <c r="H25" t="n">
-        <v>6.9</v>
+        <v>5.1</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K25" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="26">
@@ -2890,39 +2890,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.3</v>
+        <v>25.2</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="G26" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="H26" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="I26" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K26" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="27">
@@ -2937,35 +2937,35 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>27.3</v>
+        <v>26.1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="G27" t="n">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
       <c r="H27" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="I27" t="n">
         <v>1.6</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K27" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="28">
@@ -2976,39 +2976,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27.4</v>
+        <v>26.2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="G28" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="H28" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I28" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J28" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="K28" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -3023,29 +3023,29 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26.5</v>
+        <v>27.7</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="H29" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J29" t="n">
         <v>0.5</v>
@@ -3062,39 +3062,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>29.4</v>
+        <v>25.3</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="G30" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="H30" t="n">
-        <v>5.8</v>
+        <v>7.9</v>
       </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="K30" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -3105,39 +3105,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="G31" t="n">
-        <v>7.3</v>
+        <v>6.1</v>
       </c>
       <c r="H31" t="n">
-        <v>7.3</v>
+        <v>6.2</v>
       </c>
       <c r="I31" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K31" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
     </row>
   </sheetData>
@@ -3223,35 +3223,35 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19.9</v>
+        <v>21.4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="G2" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J2" t="n">
         <v>0.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="3">
@@ -3262,36 +3262,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.3</v>
+        <v>20.8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="G3" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
         <v>1.3</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="K3" t="n">
         <v>3.2</v>
@@ -3309,23 +3309,23 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>83.9</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G4" t="n">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="H4" t="n">
         <v>3.6</v>
@@ -3334,7 +3334,7 @@
         <v>1.1</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>2.8</v>
@@ -3348,39 +3348,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18.9</v>
+        <v>20.7</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="F5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K5" t="n">
         <v>2.5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2.4</v>
       </c>
     </row>
     <row r="6">
@@ -3391,39 +3391,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>8.800000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K6" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="7">
@@ -3434,39 +3434,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>18.9</v>
+        <v>19.9</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="G7" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="H7" t="n">
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="K7" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="8">
@@ -3477,36 +3477,36 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.1</v>
+        <v>21.5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="H8" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K8" t="n">
         <v>2.4</v>
@@ -3520,39 +3520,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="G9" t="n">
-        <v>6.3</v>
+        <v>6.8</v>
       </c>
       <c r="H9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="K9" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="10">
@@ -3563,39 +3563,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20.4</v>
+        <v>24</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="G10" t="n">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="H10" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K10" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="11">
@@ -3606,39 +3606,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="G11" t="n">
         <v>7</v>
       </c>
       <c r="H11" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="K11" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -3649,39 +3649,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>19.2</v>
+        <v>21.1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="G12" t="n">
-        <v>7.9</v>
+        <v>7.3</v>
       </c>
       <c r="H12" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0.7</v>
       </c>
       <c r="K12" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13">
@@ -3692,39 +3692,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.8</v>
+        <v>19.9</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="G13" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="H13" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J13" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="K13" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="14">
@@ -3735,39 +3735,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21.1</v>
+        <v>26.6</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="G14" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="15">
@@ -3778,15 +3778,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20.1</v>
+        <v>21.1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3795,22 +3795,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="G15" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="H15" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="K15" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -3821,39 +3821,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22</v>
+        <v>23.9</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G16" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K16" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="17">
@@ -3864,39 +3864,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21.7</v>
+        <v>22.1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="G17" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="H17" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="K17" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="18">
@@ -3907,39 +3907,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>28.1</v>
+        <v>21.1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="G18" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="H18" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="K18" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -3958,31 +3958,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G19" t="n">
         <v>9</v>
       </c>
       <c r="H19" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="20">
@@ -3993,39 +3993,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.7</v>
+        <v>21.4</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>83.9</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="G20" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="H20" t="n">
         <v>4.6</v>
       </c>
       <c r="I20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J20" t="n">
         <v>1.2</v>
       </c>
-      <c r="J20" t="n">
-        <v>0.7</v>
-      </c>
       <c r="K20" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="21">
@@ -4036,39 +4036,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22.5</v>
+        <v>24.2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="G21" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="H21" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I21" t="n">
         <v>1.6</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K21" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="22">
@@ -4079,39 +4079,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>25</v>
+        <v>23.6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="G22" t="n">
-        <v>9.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="H22" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K22" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="23">
@@ -4122,39 +4122,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.7</v>
+        <v>22.4</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>83.9</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="G23" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="H23" t="n">
         <v>4.5</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K23" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="24">
@@ -4165,39 +4165,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.1</v>
+        <v>25</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="G24" t="n">
-        <v>7.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K24" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="25">
@@ -4208,39 +4208,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>25.4</v>
+        <v>21.2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="G25" t="n">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="26">
@@ -4251,39 +4251,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>20.7</v>
+        <v>25.3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="G26" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I26" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="K26" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="27">
@@ -4294,39 +4294,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.9</v>
+        <v>22.5</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="G27" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="H27" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="28">
@@ -4337,39 +4337,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.4</v>
+        <v>23.9</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="G28" t="n">
-        <v>9.6</v>
+        <v>8.9</v>
       </c>
       <c r="H28" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="I28" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
         <v>1.1</v>
       </c>
       <c r="K28" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="29">
@@ -4380,39 +4380,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.1</v>
+        <v>24.4</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="G29" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="H29" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="K29" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="30">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4431,31 +4431,31 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="G30" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="H30" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="31">
@@ -4466,39 +4466,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>25.5</v>
+        <v>24.4</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="G31" t="n">
-        <v>8.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J31" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
@@ -4580,39 +4580,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20.1</v>
+        <v>20.6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>8.699999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="3">
@@ -4623,39 +4623,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.4</v>
+        <v>19.5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>10.1</v>
+        <v>9.5</v>
       </c>
       <c r="H3" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J3" t="n">
         <v>0.7</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="4">
@@ -4666,39 +4666,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20.1</v>
+        <v>21</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="G4" t="n">
-        <v>10.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="5">
@@ -4709,39 +4709,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20.3</v>
+        <v>21.4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>64.5</t>
+          <t>64.9</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="G5" t="n">
-        <v>9.9</v>
+        <v>8.9</v>
       </c>
       <c r="H5" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
         <v>1.1</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="6">
@@ -4752,39 +4752,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23.1</v>
+        <v>21.8</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="G6" t="n">
-        <v>8.300000000000001</v>
+        <v>10.6</v>
       </c>
       <c r="H6" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="K6" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="7">
@@ -4795,11 +4795,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23.8</v>
+        <v>19.3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4808,26 +4808,26 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I7" t="n">
         <v>1.6</v>
       </c>
-      <c r="G7" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.8</v>
-      </c>
       <c r="J7" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K7" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="8">
@@ -4838,39 +4838,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>24.5</v>
+        <v>19.6</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="G8" t="n">
-        <v>9.199999999999999</v>
+        <v>10.9</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="K8" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="9">
@@ -4885,35 +4885,35 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23.2</v>
+        <v>21.4</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>13.1</v>
+        <v>11.9</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="10">
@@ -4924,39 +4924,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21.4</v>
+        <v>22.4</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="G10" t="n">
-        <v>8.1</v>
+        <v>9.6</v>
       </c>
       <c r="H10" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="K10" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="11">
@@ -4967,39 +4967,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21</v>
+        <v>25.2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="G11" t="n">
-        <v>10.1</v>
+        <v>12.1</v>
       </c>
       <c r="H11" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="12">
@@ -5010,36 +5010,36 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.6</v>
+        <v>22.3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="G12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="H12" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="K12" t="n">
         <v>3</v>
@@ -5053,39 +5053,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.3</v>
+        <v>24.5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="G13" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="H13" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="K13" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -5096,39 +5096,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20.9</v>
+        <v>20.5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="G14" t="n">
-        <v>10.3</v>
+        <v>11.3</v>
       </c>
       <c r="H14" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K14" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="15">
@@ -5139,39 +5139,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.4</v>
+        <v>23.8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="G15" t="n">
-        <v>11.6</v>
+        <v>10.2</v>
       </c>
       <c r="H15" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="16">
@@ -5182,39 +5182,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>25.8</v>
+        <v>23.5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="G16" t="n">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="17">
@@ -5225,39 +5225,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.1</v>
+        <v>21.5</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="G17" t="n">
-        <v>9.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="H17" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="K17" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="18">
@@ -5268,39 +5268,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>26.7</v>
+        <v>25.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="G18" t="n">
-        <v>12.6</v>
+        <v>12.2</v>
       </c>
       <c r="H18" t="n">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="K18" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="19">
@@ -5311,39 +5311,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>25.3</v>
+        <v>23.7</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="F19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K19" t="n">
         <v>3</v>
-      </c>
-      <c r="G19" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H19" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3.3</v>
       </c>
     </row>
     <row r="20">
@@ -5354,39 +5354,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>25.7</v>
+        <v>23.4</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="G20" t="n">
-        <v>13.8</v>
+        <v>10.5</v>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="K20" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="21">
@@ -5397,36 +5397,36 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.5</v>
+        <v>24.7</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="G21" t="n">
-        <v>11.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="K21" t="n">
         <v>2.8</v>
@@ -5440,39 +5440,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>26.5</v>
+        <v>24.9</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="G22" t="n">
-        <v>8.9</v>
+        <v>10.1</v>
       </c>
       <c r="H22" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="K22" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="23">
@@ -5483,39 +5483,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>27.9</v>
+        <v>23.6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="G23" t="n">
-        <v>10.4</v>
+        <v>11.2</v>
       </c>
       <c r="H23" t="n">
         <v>3.7</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="K23" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="24">
@@ -5526,39 +5526,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>26.6</v>
+        <v>27.1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>2.8</v>
       </c>
       <c r="G24" t="n">
-        <v>9.1</v>
+        <v>13.1</v>
       </c>
       <c r="H24" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="K24" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="25">
@@ -5569,39 +5569,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.3</v>
+        <v>25.8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="G25" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="K25" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="26">
@@ -5612,33 +5612,33 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>27.1</v>
+        <v>25.3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="G26" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H26" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I26" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J26" t="n">
         <v>1.2</v>
@@ -5655,39 +5655,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>26.3</v>
+        <v>24.6</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="G27" t="n">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="H27" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="K27" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="28">
@@ -5702,35 +5702,35 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>25.9</v>
+        <v>25.5</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>2.9</v>
       </c>
       <c r="G28" t="n">
-        <v>8.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K28" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="29">
@@ -5741,39 +5741,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>23.4</v>
+        <v>27.4</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>91.1</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="G29" t="n">
-        <v>10.8</v>
+        <v>13.5</v>
       </c>
       <c r="H29" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
         <v>1.2</v>
       </c>
       <c r="K29" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="30">
@@ -5788,35 +5788,35 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>28.9</v>
+        <v>29.7</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="F30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G30" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J30" t="n">
         <v>1.9</v>
       </c>
-      <c r="G30" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="H30" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2.4</v>
-      </c>
       <c r="K30" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="31">
@@ -5827,39 +5827,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>27.4</v>
+        <v>25</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>3</v>
       </c>
       <c r="G31" t="n">
-        <v>14.3</v>
+        <v>10.8</v>
       </c>
       <c r="H31" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J31" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="K31" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
     </row>
   </sheetData>
@@ -5941,7 +5941,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -5949,31 +5949,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="G2" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="3">
@@ -5984,39 +5984,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.8</v>
+        <v>14.8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="G3" t="n">
-        <v>15.4</v>
+        <v>12.9</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="4">
@@ -6027,39 +6027,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>59.6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="G4" t="n">
-        <v>14.4</v>
+        <v>12.9</v>
       </c>
       <c r="H4" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -6070,39 +6070,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="G5" t="n">
-        <v>14.6</v>
+        <v>14.1</v>
       </c>
       <c r="H5" t="n">
         <v>3.8</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="6">
@@ -6113,39 +6113,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I6" t="n">
         <v>1.2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.3</v>
       </c>
       <c r="J6" t="n">
         <v>2.1</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="7">
@@ -6156,39 +6156,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19.9</v>
+        <v>19.3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G7" t="n">
-        <v>13.8</v>
+        <v>13.2</v>
       </c>
       <c r="H7" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="8">
@@ -6199,39 +6199,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.1</v>
+        <v>18.5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G8" t="n">
-        <v>14.8</v>
+        <v>14.5</v>
       </c>
       <c r="H8" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="9">
@@ -6242,39 +6242,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19.1</v>
+        <v>19.6</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="G9" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="H9" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="10">
@@ -6285,39 +6285,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>15.8</v>
+        <v>20.6</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="G10" t="n">
-        <v>12.9</v>
+        <v>13.6</v>
       </c>
       <c r="H10" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="11">
@@ -6332,35 +6332,35 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23.4</v>
+        <v>25.1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="G11" t="n">
-        <v>16.4</v>
+        <v>16.6</v>
       </c>
       <c r="H11" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="12">
@@ -6371,39 +6371,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="G12" t="n">
-        <v>13</v>
+        <v>14.1</v>
       </c>
       <c r="H12" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="13">
@@ -6414,39 +6414,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>19.9</v>
+        <v>20.6</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="G13" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="H13" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J13" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="14">
@@ -6457,39 +6457,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>19.9</v>
+        <v>22</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>63.6</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="G14" t="n">
-        <v>14.3</v>
+        <v>14.6</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="I14" t="n">
         <v>1.6</v>
       </c>
       <c r="J14" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="K14" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="15">
@@ -6500,39 +6500,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="G15" t="n">
-        <v>12.3</v>
+        <v>13.6</v>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="16">
@@ -6543,39 +6543,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>20.5</v>
+        <v>19.2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="G16" t="n">
-        <v>15</v>
+        <v>13.4</v>
       </c>
       <c r="H16" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="K16" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="17">
@@ -6586,39 +6586,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24.2</v>
+        <v>22</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>55.8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="G17" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="H17" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="I17" t="n">
         <v>1.3</v>
       </c>
       <c r="J17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K17" t="n">
         <v>2.8</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.7</v>
       </c>
     </row>
     <row r="18">
@@ -6629,39 +6629,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>20.1</v>
+        <v>22.2</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="G18" t="n">
-        <v>11</v>
+        <v>14.4</v>
       </c>
       <c r="H18" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="19">
@@ -6672,39 +6672,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.5</v>
+        <v>22</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="F19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I19" t="n">
         <v>1.6</v>
       </c>
-      <c r="G19" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="H19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.6</v>
-      </c>
       <c r="J19" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="K19" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="20">
@@ -6715,39 +6715,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.4</v>
+        <v>23.1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="G20" t="n">
-        <v>14.4</v>
+        <v>15.4</v>
       </c>
       <c r="H20" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J20" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="K20" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="21">
@@ -6758,39 +6758,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>21.3</v>
+        <v>21</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="G21" t="n">
-        <v>16.1</v>
+        <v>10.8</v>
       </c>
       <c r="H21" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="K21" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -6801,39 +6801,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.1</v>
+        <v>22</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>60.3</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="G22" t="n">
-        <v>14.3</v>
+        <v>13.4</v>
       </c>
       <c r="H22" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="I22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K22" t="n">
         <v>2</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2.6</v>
       </c>
     </row>
     <row r="23">
@@ -6844,39 +6844,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>25.6</v>
+        <v>24.5</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="G23" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H23" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="I23" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="K23" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="24">
@@ -6887,39 +6887,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.1</v>
+        <v>25.7</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="G24" t="n">
-        <v>15.8</v>
+        <v>17.8</v>
       </c>
       <c r="H24" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J24" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="K24" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="25">
@@ -6930,39 +6930,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.2</v>
+        <v>22.5</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>62.1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="G25" t="n">
-        <v>13</v>
+        <v>14.8</v>
       </c>
       <c r="H25" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="I25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J25" t="n">
         <v>2</v>
       </c>
-      <c r="J25" t="n">
-        <v>1.5</v>
-      </c>
       <c r="K25" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="26">
@@ -6973,39 +6973,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>20.3</v>
+        <v>25.4</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="G26" t="n">
-        <v>14.6</v>
+        <v>13.5</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="K26" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -7016,39 +7016,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>22.6</v>
+        <v>24</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="G27" t="n">
-        <v>12.9</v>
+        <v>15.9</v>
       </c>
       <c r="H27" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="K27" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -7059,39 +7059,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.2</v>
+        <v>23.9</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="G28" t="n">
-        <v>14.3</v>
+        <v>15.4</v>
       </c>
       <c r="H28" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="K28" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="29">
@@ -7102,39 +7102,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>20.8</v>
+        <v>27</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>59.9</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="G29" t="n">
-        <v>14.4</v>
+        <v>16</v>
       </c>
       <c r="H29" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="K29" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="30">
@@ -7145,39 +7145,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>25.1</v>
+        <v>24.8</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="G30" t="n">
-        <v>15</v>
+        <v>16.7</v>
       </c>
       <c r="H30" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="K30" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="31">
@@ -7188,39 +7188,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>22.1</v>
+        <v>24.2</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="G31" t="n">
-        <v>16.6</v>
+        <v>13.8</v>
       </c>
       <c r="H31" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="I31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K31" t="n">
         <v>2.4</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="K31" t="n">
-        <v>2.6</v>
       </c>
     </row>
   </sheetData>
